--- a/Received_data/Statistics/descriptors.xlsx
+++ b/Received_data/Statistics/descriptors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kirill\Desktop\Lab\KNP-analysis\Received_data\Statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7223B1AF-BE2E-42F8-B7B2-6E2DCD66F865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB55B02-BAC2-43D6-8B46-8E632C1180D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="150">
-  <si>
-    <t>sample_id</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="149">
   <si>
     <t>Ag_275</t>
   </si>
@@ -842,108 +839,108 @@
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2">
         <v>249.186903</v>
@@ -964,7 +961,7 @@
         <v>-0.44586692781991388</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I2">
         <v>4.38599849637753E-2</v>
@@ -1021,10 +1018,10 @@
         <v>1.77847850634144E-2</v>
       </c>
       <c r="AA2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AB2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC2">
         <v>2.0228600347021401E-2</v>
@@ -1036,15 +1033,15 @@
         <v>69.16</v>
       </c>
       <c r="AF2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AG2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>149.00640300000001</v>
@@ -1065,7 +1062,7 @@
         <v>-0.59485730032689688</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I3">
         <v>6.9894365303682496E-2</v>
@@ -1122,10 +1119,10 @@
         <v>1.7201997605401129E-2</v>
       </c>
       <c r="AA3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AB3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC3">
         <v>1.9883953488372089E-2</v>
@@ -1137,15 +1134,15 @@
         <v>43</v>
       </c>
       <c r="AF3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AG3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>196.44820300000001</v>
@@ -1166,7 +1163,7 @@
         <v>-0.30266482766931802</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I4">
         <v>1.7895188712250099E-2</v>
@@ -1223,10 +1220,10 @@
         <v>1.387817567873662E-2</v>
       </c>
       <c r="AA4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC4">
         <v>3.0296153846153851E-2</v>
@@ -1238,15 +1235,15 @@
         <v>33.799999999999997</v>
       </c>
       <c r="AF4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AG4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>73.468002999999996</v>
@@ -1267,7 +1264,7 @@
         <v>-0.1274388194486917</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I5">
         <v>1.7379921778299601E-2</v>
@@ -1324,10 +1321,10 @@
         <v>1.453996970395227E-2</v>
       </c>
       <c r="AA5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC5">
         <v>1.3346878097125861E-2</v>
@@ -1339,15 +1336,15 @@
         <v>30.27</v>
       </c>
       <c r="AF5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AG5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>3.456802999999907</v>
@@ -1368,7 +1365,7 @@
         <v>0.88251323624833922</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I6">
         <v>4.4705205697541002E-3</v>
@@ -1425,10 +1422,10 @@
         <v>3.4736265726469248E-2</v>
       </c>
       <c r="AA6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AB6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC6">
         <v>1.0006249999999809E-3</v>
@@ -1440,15 +1437,15 @@
         <v>16</v>
       </c>
       <c r="AF6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AG6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>65.177202999999992</v>
@@ -1469,7 +1466,7 @@
         <v>-0.36518806754467992</v>
       </c>
       <c r="H7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I7">
         <v>2.4936467230493899E-2</v>
@@ -1526,10 +1523,10 @@
         <v>1.286750061443174E-2</v>
       </c>
       <c r="AA7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AB7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC7">
         <v>2.2969289827255272E-2</v>
@@ -1541,15 +1538,15 @@
         <v>15.63</v>
       </c>
       <c r="AF7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AG7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>63.10450299999998</v>
@@ -1570,7 +1567,7 @@
         <v>0.5045529231944661</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I8">
         <v>3.2256711220928803E-2</v>
@@ -1627,10 +1624,10 @@
         <v>1.852560836437989E-2</v>
       </c>
       <c r="AA8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC8">
         <v>2.1898883374689811E-2</v>
@@ -1642,15 +1639,15 @@
         <v>16.12</v>
       </c>
       <c r="AF8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AG8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>85.904202999999981</v>
@@ -1671,7 +1668,7 @@
         <v>0.71519083270957218</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I9">
         <v>2.6997940833529199E-2</v>
@@ -1728,10 +1725,10 @@
         <v>1.7433690755321321E-2</v>
       </c>
       <c r="AA9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC9">
         <v>2.4829204006325781E-2</v>
@@ -1743,15 +1740,15 @@
         <v>18.97</v>
       </c>
       <c r="AF9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AG9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>68.631703000000002</v>
@@ -1772,7 +1769,7 @@
         <v>1.961237934280291E-2</v>
       </c>
       <c r="H10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I10">
         <v>3.9634129878190601E-2</v>
@@ -1829,10 +1826,10 @@
         <v>1.7117802841635651E-2</v>
       </c>
       <c r="AA10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AB10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC10">
         <v>4.3861793260993702E-2</v>
@@ -1844,15 +1841,15 @@
         <v>8.7550000000000008</v>
       </c>
       <c r="AF10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AG10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>22.802003000000049</v>
@@ -1873,7 +1870,7 @@
         <v>2.616805408797607E-2</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I11">
         <v>2.1702036691521799E-2</v>
@@ -1930,10 +1927,10 @@
         <v>8.2490674739634177E-3</v>
       </c>
       <c r="AA11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB11" t="s">
         <v>44</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>45</v>
       </c>
       <c r="AC11">
         <v>1.6955406753098749E-2</v>
@@ -1945,15 +1942,15 @@
         <v>7.0190000000000001</v>
       </c>
       <c r="AF11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>22.34140299999995</v>
@@ -1974,7 +1971,7 @@
         <v>0.21836419694871531</v>
       </c>
       <c r="H12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I12">
         <v>3.2726790859736399E-2</v>
@@ -2031,10 +2028,10 @@
         <v>1.399842796891152E-2</v>
       </c>
       <c r="AA12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AC12">
         <v>9.2993474714518597E-3</v>
@@ -2046,15 +2043,15 @@
         <v>12.26</v>
       </c>
       <c r="AF12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>21.650503</v>
@@ -2075,7 +2072,7 @@
         <v>0.45396567298315199</v>
       </c>
       <c r="H13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I13">
         <v>2.5834854380495501E-2</v>
@@ -2132,10 +2129,10 @@
         <v>1.3439102273597819E-2</v>
       </c>
       <c r="AA13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AB13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AC13">
         <v>2.4841541755888649E-2</v>
@@ -2147,15 +2144,15 @@
         <v>4.67</v>
       </c>
       <c r="AF13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14">
         <v>37.771502999999967</v>
@@ -2176,7 +2173,7 @@
         <v>0.52860005234399043</v>
       </c>
       <c r="H14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I14">
         <v>2.4393114839397802E-2</v>
@@ -2233,10 +2230,10 @@
         <v>1.306172667009693E-2</v>
       </c>
       <c r="AA14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AB14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AC14">
         <v>1.8407020872865259E-2</v>
@@ -2248,15 +2245,15 @@
         <v>10.54</v>
       </c>
       <c r="AF14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>20.268702999999999</v>
@@ -2277,7 +2274,7 @@
         <v>0.6301096296241977</v>
       </c>
       <c r="H15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I15">
         <v>2.2140626930361802E-2</v>
@@ -2334,10 +2331,10 @@
         <v>1.5306472282169029E-2</v>
       </c>
       <c r="AA15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AC15">
         <v>2.2959669079627671E-2</v>
@@ -2349,15 +2346,15 @@
         <v>4.835</v>
       </c>
       <c r="AF15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>16.583902999999999</v>
@@ -2378,7 +2375,7 @@
         <v>0.34485468379234652</v>
       </c>
       <c r="H16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I16">
         <v>1.8198929155520099E-2</v>
@@ -2435,10 +2432,10 @@
         <v>1.0992424856006039E-2</v>
       </c>
       <c r="AA16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AB16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AC16">
         <v>6.6573373676248101E-3</v>
@@ -2450,15 +2447,15 @@
         <v>13.22</v>
       </c>
       <c r="AF16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>101.56460299999991</v>
@@ -2479,7 +2476,7 @@
         <v>0.12680656678413979</v>
       </c>
       <c r="H17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I17">
         <v>3.5979090600298698E-2</v>
@@ -2536,10 +2533,10 @@
         <v>1.0769476044637389E-2</v>
       </c>
       <c r="AA17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AB17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AC17">
         <v>0.12315443215705919</v>
@@ -2551,15 +2548,15 @@
         <v>4.1818226999999997</v>
       </c>
       <c r="AF17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>49.056203000000039</v>
@@ -2580,7 +2577,7 @@
         <v>0.39346781977919321</v>
       </c>
       <c r="H18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I18">
         <v>2.1682120729641999E-2</v>
@@ -2637,10 +2634,10 @@
         <v>1.3088064509305041E-2</v>
       </c>
       <c r="AA18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AB18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AC18">
         <v>1.017906107187371E-2</v>
@@ -2652,15 +2649,15 @@
         <v>24.07</v>
       </c>
       <c r="AF18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19">
         <v>49.056202999999982</v>
@@ -2681,7 +2678,7 @@
         <v>0.23394423224311819</v>
       </c>
       <c r="H19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I19">
         <v>2.66315308550783E-2</v>
@@ -2738,10 +2735,10 @@
         <v>1.226929519923513E-2</v>
       </c>
       <c r="AA19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AB19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AC19">
         <v>2.941940497335702E-2</v>
@@ -2753,15 +2750,15 @@
         <v>9.0079999999999991</v>
       </c>
       <c r="AF19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20">
         <v>93.043503000000001</v>
@@ -2782,7 +2779,7 @@
         <v>-0.28977500692904462</v>
       </c>
       <c r="H20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I20">
         <v>1.69151544511143E-2</v>
@@ -2839,10 +2836,10 @@
         <v>1.3400981030542431E-2</v>
       </c>
       <c r="AA20" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB20" t="s">
         <v>54</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>55</v>
       </c>
       <c r="AC20">
         <v>4.174759825327512E-2</v>
@@ -2854,15 +2851,15 @@
         <v>11.45</v>
       </c>
       <c r="AF20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AG20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <v>158.44870299999999</v>
@@ -2883,7 +2880,7 @@
         <v>-0.69924091799700605</v>
       </c>
       <c r="H21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I21">
         <v>2.3076119865253701E-2</v>
@@ -2940,10 +2937,10 @@
         <v>1.3704919658998079E-2</v>
       </c>
       <c r="AA21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AB21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AC21">
         <v>3.3347278635255891E-2</v>
@@ -2955,15 +2952,15 @@
         <v>24.62</v>
       </c>
       <c r="AF21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AG21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B22">
         <v>90.970803000000004</v>
@@ -2984,7 +2981,7 @@
         <v>-2.6304082882795399E-3</v>
       </c>
       <c r="H22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I22">
         <v>2.1765529559220599E-2</v>
@@ -3041,10 +3038,10 @@
         <v>1.251327250523146E-2</v>
       </c>
       <c r="AA22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AB22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AC22">
         <v>1.9892218060757388E-2</v>
@@ -3056,15 +3053,15 @@
         <v>24.03</v>
       </c>
       <c r="AF22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AG22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23">
         <v>27.177703000000001</v>
@@ -3085,7 +3082,7 @@
         <v>0.61986131023300839</v>
       </c>
       <c r="H23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I23">
         <v>1.96973246724374E-2</v>
@@ -3142,10 +3139,10 @@
         <v>1.202113822756192E-2</v>
       </c>
       <c r="AA23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AB23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AC23">
         <v>2.08168245765145E-2</v>
@@ -3157,15 +3154,15 @@
         <v>6.9660000000000002</v>
       </c>
       <c r="AF23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AG23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24">
         <v>23.262603000000041</v>
@@ -3186,7 +3183,7 @@
         <v>0.36127857042763889</v>
       </c>
       <c r="H24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I24">
         <v>2.75638162985417E-2</v>
@@ -3243,10 +3240,10 @@
         <v>1.2172115821390529E-2</v>
       </c>
       <c r="AA24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AB24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AC24">
         <v>5.0649207168980602E-2</v>
@@ -3258,15 +3255,15 @@
         <v>2.4484094999999999</v>
       </c>
       <c r="AF24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AG24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B25">
         <v>26.717102999999948</v>
@@ -3287,7 +3284,7 @@
         <v>0.37003846566909449</v>
       </c>
       <c r="H25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I25">
         <v>2.04179035903151E-2</v>
@@ -3344,10 +3341,10 @@
         <v>1.4536365450164949E-2</v>
       </c>
       <c r="AA25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AB25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AC25">
         <v>2.699343955014058E-2</v>
@@ -3359,15 +3356,15 @@
         <v>5.335</v>
       </c>
       <c r="AF25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AG25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B26">
         <v>60.340903000000033</v>
@@ -3388,7 +3385,7 @@
         <v>0.58952385387092576</v>
       </c>
       <c r="H26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I26">
         <v>2.0984315470706501E-2</v>
@@ -3445,10 +3442,10 @@
         <v>1.166607433494308E-2</v>
       </c>
       <c r="AA26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AB26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AC26">
         <v>3.2692738568082323E-2</v>
@@ -3460,15 +3457,15 @@
         <v>9.8190000000000008</v>
       </c>
       <c r="AF26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AG26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B27">
         <v>42.838103000000046</v>
@@ -3489,7 +3486,7 @@
         <v>-8.7742510198179247E-2</v>
       </c>
       <c r="H27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I27">
         <v>1.69548584281661E-2</v>
@@ -3546,10 +3543,10 @@
         <v>1.311763186803061E-2</v>
       </c>
       <c r="AA27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AB27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AC27">
         <v>2.9340829778984091E-2</v>
@@ -3561,15 +3558,15 @@
         <v>7.7370000000000001</v>
       </c>
       <c r="AF27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AG27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B28">
         <v>38.923002999999952</v>
@@ -3590,7 +3587,7 @@
         <v>0.75340145745909926</v>
       </c>
       <c r="H28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I28">
         <v>9.3919132085930005E-3</v>
@@ -3647,10 +3644,10 @@
         <v>1.8223772172691419E-2</v>
       </c>
       <c r="AA28" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB28" t="s">
         <v>63</v>
-      </c>
-      <c r="AB28" t="s">
-        <v>64</v>
       </c>
       <c r="AC28">
         <v>1.012706913339825E-2</v>
@@ -3662,15 +3659,15 @@
         <v>20.54</v>
       </c>
       <c r="AF28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B29">
         <v>47.444103000000048</v>
@@ -3691,7 +3688,7 @@
         <v>0.17876171161146989</v>
       </c>
       <c r="H29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I29">
         <v>1.1630470575517001E-2</v>
@@ -3748,10 +3745,10 @@
         <v>1.245627954893533E-2</v>
       </c>
       <c r="AA29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AB29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC29">
         <v>2.1293965517241401E-2</v>
@@ -3763,15 +3760,15 @@
         <v>11.6</v>
       </c>
       <c r="AF29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B30">
         <v>66.559003000000331</v>
@@ -3792,7 +3789,7 @@
         <v>4.594906150302954</v>
       </c>
       <c r="H30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I30">
         <v>2.4341328622265599E-2</v>
@@ -3849,10 +3846,10 @@
         <v>7.3188673405238918E-3</v>
       </c>
       <c r="AA30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AB30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC30">
         <v>2.3024742268041291E-2</v>
@@ -3864,15 +3861,15 @@
         <v>14.55</v>
       </c>
       <c r="AF30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B31">
         <v>72.777102999999997</v>
@@ -3893,7 +3890,7 @@
         <v>-0.1975225949770483</v>
       </c>
       <c r="H31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I31">
         <v>1.4716851306978499E-2</v>
@@ -3950,10 +3947,10 @@
         <v>1.2193699486519679E-2</v>
       </c>
       <c r="AA31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AB31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC31">
         <v>2.242341292952825E-2</v>
@@ -3965,15 +3962,15 @@
         <v>17.170000000000002</v>
       </c>
       <c r="AF31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B32">
         <v>38.462402999999981</v>
@@ -3994,7 +3991,7 @@
         <v>0.1778514446518189</v>
       </c>
       <c r="H32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I32">
         <v>2.0839852370285301E-2</v>
@@ -4051,10 +4048,10 @@
         <v>1.2510868765513661E-2</v>
       </c>
       <c r="AA32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AB32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC32">
         <v>2.770920794850263E-2</v>
@@ -4066,15 +4063,15 @@
         <v>7.1459999999999999</v>
       </c>
       <c r="AF32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B33">
         <v>29.711003000000002</v>
@@ -4095,7 +4092,7 @@
         <v>0.114936958792331</v>
       </c>
       <c r="H33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I33">
         <v>1.5729538527257302E-2</v>
@@ -4152,10 +4149,10 @@
         <v>1.0550898028233439E-2</v>
       </c>
       <c r="AA33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AB33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC33">
         <v>2.4303857008466601E-2</v>
@@ -4167,15 +4164,15 @@
         <v>6.3780000000000001</v>
       </c>
       <c r="AF33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B34">
         <v>19.117202999999979</v>
@@ -4196,7 +4193,7 @@
         <v>-0.25661576400976083</v>
       </c>
       <c r="H34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I34">
         <v>2.1838536689390699E-2</v>
@@ -4253,10 +4250,10 @@
         <v>1.2506544479543609E-2</v>
       </c>
       <c r="AA34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AB34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC34">
         <v>1.962863190302095E-2</v>
@@ -4268,15 +4265,15 @@
         <v>5.1970000000000001</v>
       </c>
       <c r="AF34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B35">
         <v>30.63220300000005</v>
@@ -4297,7 +4294,7 @@
         <v>-8.7147480258980003E-2</v>
       </c>
       <c r="H35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I35">
         <v>2.08068343216633E-2</v>
@@ -4354,10 +4351,10 @@
         <v>1.148566696597585E-2</v>
       </c>
       <c r="AA35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AB35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC35">
         <v>2.5833597464342349E-2</v>
@@ -4369,15 +4366,15 @@
         <v>6.31</v>
       </c>
       <c r="AF35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B36">
         <v>41.916902999999998</v>
@@ -4398,7 +4395,7 @@
         <v>1.4246381980445481E-2</v>
       </c>
       <c r="H36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I36">
         <v>1.5674557136700001E-2</v>
@@ -4455,10 +4452,10 @@
         <v>1.173679945977942E-2</v>
       </c>
       <c r="AA36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AB36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC36">
         <v>2.3879430345861419E-2</v>
@@ -4470,15 +4467,15 @@
         <v>9.3390000000000004</v>
       </c>
       <c r="AF36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B37">
         <v>64.486302999999978</v>
@@ -4499,7 +4496,7 @@
         <v>0.21743820297778171</v>
       </c>
       <c r="H37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I37">
         <v>1.04286827378797E-2</v>
@@ -4556,10 +4553,10 @@
         <v>1.2986096725956631E-2</v>
       </c>
       <c r="AA37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AB37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC37">
         <v>2.2332674571804999E-2</v>
@@ -4571,15 +4568,15 @@
         <v>15.18</v>
       </c>
       <c r="AF37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B38">
         <v>30.171602999999969</v>
@@ -4600,7 +4597,7 @@
         <v>-0.47108237549744819</v>
       </c>
       <c r="H38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I38">
         <v>9.9467764658099991E-3</v>
@@ -4657,10 +4654,10 @@
         <v>8.3014863618397338E-3</v>
       </c>
       <c r="AA38" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB38" t="s">
         <v>74</v>
-      </c>
-      <c r="AB38" t="s">
-        <v>75</v>
       </c>
       <c r="AC38">
         <v>5.4566798941798906E-3</v>
@@ -4672,15 +4669,15 @@
         <v>30.24</v>
       </c>
       <c r="AF38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AG38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B39">
         <v>21.420203000000001</v>
@@ -4701,7 +4698,7 @@
         <v>-7.1884946040817521E-2</v>
       </c>
       <c r="H39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I39">
         <v>2.1507276437869201E-2</v>
@@ -4758,10 +4755,10 @@
         <v>1.185127118857331E-2</v>
       </c>
       <c r="AA39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AB39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC39">
         <v>1.758194278903458E-2</v>
@@ -4773,15 +4770,15 @@
         <v>6.7119999999999997</v>
       </c>
       <c r="AF39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AG39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B40">
         <v>70.934703000000013</v>
@@ -4802,7 +4799,7 @@
         <v>0.66725870266869691</v>
       </c>
       <c r="H40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I40">
         <v>1.84356870319991E-2</v>
@@ -4859,10 +4856,10 @@
         <v>1.4002301575314419E-2</v>
       </c>
       <c r="AA40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC40">
         <v>1.695181778361805E-2</v>
@@ -4874,15 +4871,15 @@
         <v>22.83</v>
       </c>
       <c r="AF40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AG40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B41">
         <v>26.71710299999997</v>
@@ -4903,7 +4900,7 @@
         <v>-0.53222744044599191</v>
       </c>
       <c r="H41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I41">
         <v>1.94743589349139E-2</v>
@@ -4960,10 +4957,10 @@
         <v>1.8003595518282369E-2</v>
       </c>
       <c r="AA41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AB41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC41">
         <v>1.3949901768172891E-2</v>
@@ -4975,15 +4972,15 @@
         <v>10.18</v>
       </c>
       <c r="AF41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AG41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B42">
         <v>22.571702999999999</v>
@@ -5004,7 +5001,7 @@
         <v>-1.051736827294131</v>
       </c>
       <c r="H42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I42">
         <v>1.35016907475588E-2</v>
@@ -5061,10 +5058,10 @@
         <v>1.099704783820484E-2</v>
       </c>
       <c r="AA42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC42">
         <v>1.3959954233409609E-2</v>
@@ -5076,15 +5073,15 @@
         <v>8.74</v>
       </c>
       <c r="AF42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AG42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B43">
         <v>18.656603</v>
@@ -5105,7 +5102,7 @@
         <v>-0.24295504863136941</v>
       </c>
       <c r="H43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I43">
         <v>2.1106426309438299E-2</v>
@@ -5162,10 +5159,10 @@
         <v>1.8866527031758659E-2</v>
       </c>
       <c r="AA43" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB43" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC43">
         <v>1.5105428443248079E-2</v>
@@ -5177,15 +5174,15 @@
         <v>6.6870000000000003</v>
       </c>
       <c r="AF43" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AG43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B44">
         <v>20.268702999999999</v>
@@ -5206,7 +5203,7 @@
         <v>0.40583807007946771</v>
       </c>
       <c r="H44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I44">
         <v>1.6089700657621799E-2</v>
@@ -5263,10 +5260,10 @@
         <v>6.7409471913140668E-3</v>
       </c>
       <c r="AA44" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AB44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC44">
         <v>1.638016528925618E-2</v>
@@ -5278,15 +5275,15 @@
         <v>6.6550000000000002</v>
       </c>
       <c r="AF44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AG44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B45">
         <v>18.196003000000001</v>
@@ -5307,7 +5304,7 @@
         <v>-6.1271648485929919E-2</v>
       </c>
       <c r="H45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I45">
         <v>1.3411946304543799E-2</v>
@@ -5364,10 +5361,10 @@
         <v>7.2892939747372472E-3</v>
       </c>
       <c r="AA45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AB45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC45">
         <v>1.18641810918775E-2</v>
@@ -5379,15 +5376,15 @@
         <v>8.2609999999999992</v>
       </c>
       <c r="AF45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AG45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B46">
         <v>28.098902999999861</v>
@@ -5408,7 +5405,7 @@
         <v>1.145553212430255</v>
       </c>
       <c r="H46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I46">
         <v>1.8536168126828199E-2</v>
@@ -5465,10 +5462,10 @@
         <v>1.278352111395442E-2</v>
       </c>
       <c r="AA46" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC46">
         <v>2.4713641676406699E-2</v>
@@ -5480,15 +5477,15 @@
         <v>5.9889999999999999</v>
       </c>
       <c r="AF46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AG46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B47">
         <v>51.589503000000022</v>
@@ -5509,7 +5506,7 @@
         <v>0.18763351538180831</v>
       </c>
       <c r="H47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I47">
         <v>2.74604833888525E-2</v>
@@ -5566,10 +5563,10 @@
         <v>1.1904686845285979E-2</v>
       </c>
       <c r="AA47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC47">
         <v>2.7597428288822948E-2</v>
@@ -5581,15 +5578,15 @@
         <v>10.11</v>
       </c>
       <c r="AF47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AG47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B48">
         <v>48.595602999999997</v>
@@ -5610,7 +5607,7 @@
         <v>-0.22788851016098241</v>
       </c>
       <c r="H48" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I48">
         <v>2.7924079653127602E-2</v>
@@ -5667,10 +5664,10 @@
         <v>2.0965712672571701E-2</v>
       </c>
       <c r="AA48" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB48" t="s">
         <v>85</v>
-      </c>
-      <c r="AB48" t="s">
-        <v>86</v>
       </c>
       <c r="AC48">
         <v>2.2494524010109519E-2</v>
@@ -5682,15 +5679,15 @@
         <v>11.87</v>
       </c>
       <c r="AF48" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG48" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B49">
         <v>52.741002999999971</v>
@@ -5711,7 +5708,7 @@
         <v>-8.7682619339422452E-2</v>
       </c>
       <c r="H49" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I49">
         <v>2.7603791252383401E-2</v>
@@ -5768,10 +5765,10 @@
         <v>1.3443128401923779E-2</v>
       </c>
       <c r="AA49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AB49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AC49">
         <v>2.3406779661016942E-2</v>
@@ -5783,15 +5780,15 @@
         <v>12.39</v>
       </c>
       <c r="AF49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG49" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B50">
         <v>18.886903000000022</v>
@@ -5812,7 +5809,7 @@
         <v>0.34973380159844369</v>
       </c>
       <c r="H50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I50">
         <v>2.3862897859949699E-2</v>
@@ -5869,10 +5866,10 @@
         <v>1.497761044668852E-2</v>
       </c>
       <c r="AA50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AB50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AC50">
         <v>1.9343500092988689E-2</v>
@@ -5884,15 +5881,15 @@
         <v>5.3769999999999998</v>
       </c>
       <c r="AF50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B51">
         <v>17.505102999999991</v>
@@ -5913,7 +5910,7 @@
         <v>0.53394579254945285</v>
       </c>
       <c r="H51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I51">
         <v>3.1108639293337799E-2</v>
@@ -5970,10 +5967,10 @@
         <v>9.8155649440942218E-3</v>
       </c>
       <c r="AA51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AB51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AC51">
         <v>4.6426081838734999E-2</v>
@@ -5985,15 +5982,15 @@
         <v>2.0895581999999999</v>
       </c>
       <c r="AF51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B52">
         <v>18.886903</v>
@@ -6014,7 +6011,7 @@
         <v>-0.1157453162076623</v>
       </c>
       <c r="H52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I52">
         <v>2.34443163559779E-2</v>
@@ -6071,10 +6068,10 @@
         <v>1.099242485600564E-2</v>
       </c>
       <c r="AA52" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AB52" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AC52">
         <v>2.1396831927586919E-2</v>
@@ -6086,15 +6083,15 @@
         <v>4.8609999999999998</v>
       </c>
       <c r="AF52" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B53">
         <v>32.935202999999987</v>
@@ -6115,7 +6112,7 @@
         <v>-0.95251957817177324</v>
       </c>
       <c r="H53" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I53">
         <v>2.7357054923085999E-2</v>
@@ -6172,10 +6169,10 @@
         <v>7.2470714754275826E-3</v>
       </c>
       <c r="AA53" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AB53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AC53">
         <v>2.9673278879813299E-2</v>
@@ -6187,15 +6184,15 @@
         <v>5.9989999999999997</v>
       </c>
       <c r="AF53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG53" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B54">
         <v>46.753203000000013</v>
@@ -6216,7 +6213,7 @@
         <v>0.28813958772532539</v>
       </c>
       <c r="H54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I54">
         <v>3.1695787170354699E-2</v>
@@ -6273,10 +6270,10 @@
         <v>1.418237653389103E-2</v>
       </c>
       <c r="AA54" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AC54">
         <v>3.2747864354128922E-2</v>
@@ -6288,15 +6285,15 @@
         <v>7.726</v>
       </c>
       <c r="AF54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B55">
         <v>103.637303</v>
@@ -6317,7 +6314,7 @@
         <v>-0.49260397691615587</v>
       </c>
       <c r="H55" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I55">
         <v>1.9218955848218901E-2</v>
@@ -6374,10 +6371,10 @@
         <v>1.7221023401902329E-2</v>
       </c>
       <c r="AA55" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB55" t="s">
         <v>93</v>
-      </c>
-      <c r="AB55" t="s">
-        <v>94</v>
       </c>
       <c r="AC55">
         <v>2.261799591002045E-2</v>
@@ -6389,15 +6386,15 @@
         <v>24.45</v>
       </c>
       <c r="AF55" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG55" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B56">
         <v>37.310902999999968</v>
@@ -6418,7 +6415,7 @@
         <v>-0.42358780700145798</v>
       </c>
       <c r="H56" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I56">
         <v>2.5767366817971399E-2</v>
@@ -6475,10 +6472,10 @@
         <v>1.429095335646614E-2</v>
       </c>
       <c r="AA56" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AB56" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC56">
         <v>2.779042971397587E-2</v>
@@ -6490,15 +6487,15 @@
         <v>7.3769999999999998</v>
       </c>
       <c r="AF56" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG56" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B57">
         <v>56.886402999999987</v>
@@ -6519,7 +6516,7 @@
         <v>0.44475863341378391</v>
       </c>
       <c r="H57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I57">
         <v>2.4133304044278901E-2</v>
@@ -6576,10 +6573,10 @@
         <v>1.09988866685732E-2</v>
       </c>
       <c r="AA57" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AB57" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC57">
         <v>2.1752333094041631E-2</v>
@@ -6591,15 +6588,15 @@
         <v>13.93</v>
       </c>
       <c r="AF57" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B58">
         <v>35.468502999999998</v>
@@ -6620,7 +6617,7 @@
         <v>0.41191071760150783</v>
       </c>
       <c r="H58" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I58">
         <v>1.8006855294774599E-2</v>
@@ -6677,10 +6674,10 @@
         <v>9.326421096272337E-3</v>
       </c>
       <c r="AA58" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AB58" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC58">
         <v>2.092953356339753E-2</v>
@@ -6692,15 +6689,15 @@
         <v>8.9830000000000005</v>
       </c>
       <c r="AF58" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG58" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B59">
         <v>38.232102999999981</v>
@@ -6721,7 +6718,7 @@
         <v>1.036698120459848</v>
       </c>
       <c r="H59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I59">
         <v>2.32101609647519E-2</v>
@@ -6778,10 +6775,10 @@
         <v>1.3324630544804331E-2</v>
       </c>
       <c r="AA59" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AB59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC59">
         <v>2.2255480137977068E-2</v>
@@ -6793,15 +6790,15 @@
         <v>8.9870000000000001</v>
       </c>
       <c r="AF59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B60">
         <v>26.94740299999998</v>
@@ -6822,7 +6819,7 @@
         <v>-1.1512532190585341</v>
       </c>
       <c r="H60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I60">
         <v>1.68410891033237E-2</v>
@@ -6879,10 +6876,10 @@
         <v>7.945688845547012E-3</v>
       </c>
       <c r="AA60" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AB60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC60">
         <v>1.7299717826033619E-2</v>
@@ -6894,15 +6891,15 @@
         <v>8.1509999999999998</v>
       </c>
       <c r="AF60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B61">
         <v>43.989603000000002</v>
@@ -6923,7 +6920,7 @@
         <v>0.1999641567977353</v>
       </c>
       <c r="H61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I61">
         <v>2.4627490030579301E-2</v>
@@ -6980,10 +6977,10 @@
         <v>1.9875683318879341E-2</v>
       </c>
       <c r="AA61" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AB61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC61">
         <v>2.6503088152723189E-2</v>
@@ -6995,15 +6992,15 @@
         <v>8.9049999999999994</v>
       </c>
       <c r="AF61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B62">
         <v>45.832003000000022</v>
@@ -7024,7 +7021,7 @@
         <v>1.938486655089612</v>
       </c>
       <c r="H62" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I62">
         <v>2.4099466991246401E-2</v>
@@ -7081,10 +7078,10 @@
         <v>1.2732290952657431E-2</v>
       </c>
       <c r="AA62" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AB62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC62">
         <v>2.4645287688183141E-2</v>
@@ -7096,15 +7093,15 @@
         <v>9.6980000000000004</v>
       </c>
       <c r="AF62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG62" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B63">
         <v>45.141102999999973</v>
@@ -7125,7 +7122,7 @@
         <v>0.74217071987972982</v>
       </c>
       <c r="H63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I63">
         <v>2.5672991114581999E-2</v>
@@ -7182,10 +7179,10 @@
         <v>2.061072181341058E-2</v>
       </c>
       <c r="AA63" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AB63" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC63">
         <v>2.562322797437782E-2</v>
@@ -7197,15 +7194,15 @@
         <v>9.5229999999999997</v>
       </c>
       <c r="AF63" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B64">
         <v>99.952503000000007</v>
@@ -7226,7 +7223,7 @@
         <v>-8.8010926797648992E-2</v>
       </c>
       <c r="H64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I64">
         <v>1.5910676531856401E-2</v>
@@ -7283,10 +7280,10 @@
         <v>1.5503500676944341E-2</v>
       </c>
       <c r="AA64" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB64" t="s">
         <v>103</v>
-      </c>
-      <c r="AB64" t="s">
-        <v>104</v>
       </c>
       <c r="AC64">
         <v>2.4904326923076921E-2</v>
@@ -7298,15 +7295,15 @@
         <v>20.8</v>
       </c>
       <c r="AF64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B65">
         <v>36.850302999999982</v>
@@ -7327,7 +7324,7 @@
         <v>0.47477432807084702</v>
       </c>
       <c r="H65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I65">
         <v>1.7553083548465999E-2</v>
@@ -7384,10 +7381,10 @@
         <v>1.360379659549513E-2</v>
       </c>
       <c r="AA65" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AB65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AC65">
         <v>2.0467662709783029E-2</v>
@@ -7399,15 +7396,15 @@
         <v>9.7720000000000002</v>
       </c>
       <c r="AF65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B66">
         <v>20.959603000000001</v>
@@ -7428,7 +7425,7 @@
         <v>0.81033380159846713</v>
       </c>
       <c r="H66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I66">
         <v>2.3503470144218198E-2</v>
@@ -7485,10 +7482,10 @@
         <v>1.497761044668826E-2</v>
       </c>
       <c r="AA66" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AB66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AC66">
         <v>1.4151012442059021E-2</v>
@@ -7500,15 +7497,15 @@
         <v>8.1980000000000004</v>
       </c>
       <c r="AF66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B67">
         <v>36.850302999999997</v>
@@ -7529,7 +7526,7 @@
         <v>4.7948501507304009E-2</v>
       </c>
       <c r="H67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I67">
         <v>1.8714247603032998E-2</v>
@@ -7586,10 +7583,10 @@
         <v>1.2728925485855601E-2</v>
       </c>
       <c r="AA67" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AC67">
         <v>1.1275354107648719E-2</v>
@@ -7601,15 +7598,15 @@
         <v>17.649999999999999</v>
       </c>
       <c r="AF67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B68">
         <v>18.656602999999979</v>
@@ -7630,7 +7627,7 @@
         <v>9.0754972431377645E-2</v>
       </c>
       <c r="H68" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I68">
         <v>1.53105088369139E-2</v>
@@ -7687,10 +7684,10 @@
         <v>9.3228978708055511E-3</v>
       </c>
       <c r="AA68" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AB68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AC68">
         <v>1.430915976995371E-2</v>
@@ -7702,15 +7699,15 @@
         <v>7.1289999999999996</v>
       </c>
       <c r="AF68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG68" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B69">
         <v>15.662702999999979</v>
@@ -7731,7 +7728,7 @@
         <v>0.25532401906501478</v>
       </c>
       <c r="H69" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I69">
         <v>1.1658917871353799E-2</v>
@@ -7788,10 +7785,10 @@
         <v>1.7417154453152971E-2</v>
       </c>
       <c r="AA69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB69" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AC69">
         <v>9.5646916565900846E-3</v>
@@ -7803,15 +7800,15 @@
         <v>9.0969999999999995</v>
       </c>
       <c r="AF69" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG69" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B70">
         <v>17.96570299999998</v>
@@ -7832,7 +7829,7 @@
         <v>9.0754972431377645E-2</v>
       </c>
       <c r="H70" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I70">
         <v>1.4247618525881399E-2</v>
@@ -7889,10 +7886,10 @@
         <v>9.3228978708055511E-3</v>
       </c>
       <c r="AA70" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AB70" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AC70">
         <v>1.503796337650737E-2</v>
@@ -7904,15 +7901,15 @@
         <v>6.7169999999999996</v>
       </c>
       <c r="AF70" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG70" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B71">
         <v>19.577802999999971</v>
@@ -7933,7 +7930,7 @@
         <v>0.37352852918339702</v>
       </c>
       <c r="H71" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I71">
         <v>1.18676365295525E-2</v>
@@ -7990,10 +7987,10 @@
         <v>1.099440563918282E-2</v>
       </c>
       <c r="AA71" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AB71" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AC71">
         <v>1.493901603398656E-2</v>
@@ -8005,15 +8002,15 @@
         <v>7.2969999999999997</v>
       </c>
       <c r="AF71" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG71" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B72">
         <v>20.268702999999999</v>
@@ -8034,7 +8031,7 @@
         <v>0.34896621847845122</v>
       </c>
       <c r="H72" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I72">
         <v>1.38060280968048E-2</v>
@@ -8091,10 +8088,10 @@
         <v>9.6151945943883238E-3</v>
       </c>
       <c r="AA72" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AB72" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AC72">
         <v>1.414803587217379E-2</v>
@@ -8106,15 +8103,15 @@
         <v>7.9169999999999998</v>
       </c>
       <c r="AF72" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG72" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B73">
         <v>3.22650299999993</v>
@@ -8135,7 +8132,7 @@
         <v>0.25489311571158918</v>
       </c>
       <c r="H73" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I73">
         <v>5.6638985010858999E-3</v>
@@ -8192,10 +8189,10 @@
         <v>6.4293472224067356E-3</v>
       </c>
       <c r="AA73" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB73" t="s">
         <v>113</v>
-      </c>
-      <c r="AB73" t="s">
-        <v>114</v>
       </c>
       <c r="AC73">
         <v>9.2042318307267255E-3</v>
@@ -8207,15 +8204,15 @@
         <v>2.1739999999999999</v>
       </c>
       <c r="AF73" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG73" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B74">
         <v>2.5844371399708548</v>
@@ -8236,7 +8233,7 @@
         <v>-2.3743960313473481E-2</v>
       </c>
       <c r="H74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I74">
         <v>6.6739996643025001E-3</v>
@@ -8293,10 +8290,10 @@
         <v>1.256138049823833E-2</v>
       </c>
       <c r="AA74" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AB74" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AC74">
         <v>8.2536270194336486E-3</v>
@@ -8308,15 +8305,15 @@
         <v>1.8009999999999999</v>
       </c>
       <c r="AF74" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B75">
         <v>0.80431898319776673</v>
@@ -8337,7 +8334,7 @@
         <v>-7.2007194178935752E-3</v>
       </c>
       <c r="H75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I75">
         <v>3.6417304226800001E-3</v>
@@ -8394,10 +8391,10 @@
         <v>3.692162485440278E-3</v>
       </c>
       <c r="AA75" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AB75" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AC75">
         <v>5.9951924479465079E-3</v>
@@ -8409,15 +8406,15 @@
         <v>0.86929999999999996</v>
       </c>
       <c r="AF75" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B76">
         <v>0.99299782647700596</v>
@@ -8438,7 +8435,7 @@
         <v>-3.7358230431360222E-3</v>
       </c>
       <c r="H76" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I76">
         <v>1.9508779704592999E-3</v>
@@ -8495,10 +8492,10 @@
         <v>3.7702533487155832E-3</v>
       </c>
       <c r="AA76" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AB76" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AC76">
         <v>7.6550584912881614E-3</v>
@@ -8510,15 +8507,15 @@
         <v>0.67149999999999999</v>
       </c>
       <c r="AF76" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG76" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B77">
         <v>0.48644329701665351</v>
@@ -8539,7 +8536,7 @@
         <v>6.5555597559618373E-3</v>
       </c>
       <c r="H77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I77">
         <v>2.2531544556317999E-3</v>
@@ -8596,10 +8593,10 @@
         <v>6.902826197948464E-3</v>
       </c>
       <c r="AA77" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AB77" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AC77">
         <v>3.327107351131509E-3</v>
@@ -8611,15 +8608,15 @@
         <v>0.91020000000000001</v>
       </c>
       <c r="AF77" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B78">
         <v>14.741503</v>
@@ -8640,7 +8637,7 @@
         <v>-0.77839307593621943</v>
       </c>
       <c r="H78" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I78">
         <v>1.46466033125552E-2</v>
@@ -8697,10 +8694,10 @@
         <v>5.2118823127248349E-3</v>
       </c>
       <c r="AA78" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AB78" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AC78">
         <v>1.345681063122922E-2</v>
@@ -8712,15 +8709,15 @@
         <v>6.02</v>
       </c>
       <c r="AF78" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG78" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B79">
         <v>1.18629647305119</v>
@@ -8741,7 +8738,7 @@
         <v>-1.209104954740914E-2</v>
       </c>
       <c r="H79" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I79">
         <v>2.9399029784613001E-3</v>
@@ -8798,10 +8795,10 @@
         <v>5.1217079336939048E-3</v>
       </c>
       <c r="AA79" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AB79" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AC79">
         <v>7.9942472624689679E-3</v>
@@ -8813,15 +8810,15 @@
         <v>0.88619999999999999</v>
       </c>
       <c r="AF79" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG79" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B80">
         <v>1.280114430307586</v>
@@ -8842,7 +8839,7 @@
         <v>-1.0433455754214839E-2</v>
       </c>
       <c r="H80" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I80">
         <v>3.4060740951122001E-3</v>
@@ -8899,10 +8896,10 @@
         <v>1.577829596057729E-3</v>
       </c>
       <c r="AA80" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AB80" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AC80">
         <v>5.4902855177584847E-3</v>
@@ -8914,15 +8911,15 @@
         <v>1.2669999999999999</v>
       </c>
       <c r="AF80" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG80" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B81">
         <v>1.3977004792118679</v>
@@ -8943,7 +8940,7 @@
         <v>-1.420450348288654E-2</v>
       </c>
       <c r="H81" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I81">
         <v>4.9240590595486999E-3</v>
@@ -9000,10 +8997,10 @@
         <v>9.1664855266458123E-3</v>
       </c>
       <c r="AA81" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AB81" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AC81">
         <v>2.9247853607571889E-3</v>
@@ -9015,15 +9012,15 @@
         <v>2.7469999999999999</v>
       </c>
       <c r="AF81" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG81" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="82" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B82">
         <v>23.723202999999948</v>
@@ -9044,7 +9041,7 @@
         <v>9.9763172705815251E-2</v>
       </c>
       <c r="H82" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I82">
         <v>2.19314633096022E-2</v>
@@ -9101,10 +9098,10 @@
         <v>1.0997047838204949E-2</v>
       </c>
       <c r="AA82" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB82" t="s">
         <v>123</v>
-      </c>
-      <c r="AB82" t="s">
-        <v>124</v>
       </c>
       <c r="AC82">
         <v>2.3141687433250249E-2</v>
@@ -9116,15 +9113,15 @@
         <v>5.6180000000000003</v>
       </c>
       <c r="AF82" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG82" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B83">
         <v>26.256502999999949</v>
@@ -9145,7 +9142,7 @@
         <v>-0.27898928239849052</v>
       </c>
       <c r="H83" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I83">
         <v>1.6026383089829399E-2</v>
@@ -9202,10 +9199,10 @@
         <v>9.3264210962721288E-3</v>
       </c>
       <c r="AA83" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AB83" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AC83">
         <v>2.5587761674718199E-2</v>
@@ -9217,15 +9214,15 @@
         <v>5.5890000000000004</v>
       </c>
       <c r="AF83" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG83" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B84">
         <v>25.335303000000071</v>
@@ -9246,7 +9243,7 @@
         <v>0.30606782957539469</v>
       </c>
       <c r="H84" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I84">
         <v>1.6839430977497301E-2</v>
@@ -9303,10 +9300,10 @@
         <v>1.250942698761477E-2</v>
       </c>
       <c r="AA84" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AB84" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AC84">
         <v>2.4704105207037551E-2</v>
@@ -9318,15 +9315,15 @@
         <v>5.6269999999999998</v>
       </c>
       <c r="AF84" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG84" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B85">
         <v>25.565602999999971</v>
@@ -9347,7 +9344,7 @@
         <v>-0.20413194591203521</v>
       </c>
       <c r="H85" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I85">
         <v>1.6060394396754E-2</v>
@@ -9404,10 +9401,10 @@
         <v>8.2490674739634333E-3</v>
       </c>
       <c r="AA85" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AB85" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AC85">
         <v>2.9481996209728349E-2</v>
@@ -9419,15 +9416,15 @@
         <v>4.7489999999999997</v>
       </c>
       <c r="AF85" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG85" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="86" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B86">
         <v>34.086703000000021</v>
@@ -9448,7 +9445,7 @@
         <v>4.2758353630965473E-2</v>
       </c>
       <c r="H86" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I86">
         <v>1.5998818890829498E-2</v>
@@ -9505,10 +9502,10 @@
         <v>1.1674292357072709E-2</v>
       </c>
       <c r="AA86" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AB86" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AC86">
         <v>3.4716148830072902E-2</v>
@@ -9520,15 +9517,15 @@
         <v>5.2140000000000004</v>
       </c>
       <c r="AF86" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG86" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B87">
         <v>25.335303000000021</v>
@@ -9549,7 +9546,7 @@
         <v>0.38956131023300689</v>
       </c>
       <c r="H87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I87">
         <v>1.9351706815909499E-2</v>
@@ -9606,10 +9603,10 @@
         <v>1.2021138227561869E-2</v>
       </c>
       <c r="AA87" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AB87" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AC87">
         <v>2.5348751156336759E-2</v>
@@ -9621,15 +9618,15 @@
         <v>5.4050000000000002</v>
       </c>
       <c r="AF87" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B88">
         <v>26.256502999999949</v>
@@ -9650,7 +9647,7 @@
         <v>-6.529624857536831E-3</v>
       </c>
       <c r="H88" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I88">
         <v>1.48344081193025E-2</v>
@@ -9707,10 +9704,10 @@
         <v>1.298314211704335E-2</v>
       </c>
       <c r="AA88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AB88" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AC88">
         <v>2.716432286649971E-2</v>
@@ -9722,15 +9719,15 @@
         <v>5.1909999999999998</v>
       </c>
       <c r="AF88" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG88" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="89" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B89">
         <v>26.947403000000019</v>
@@ -9751,7 +9748,7 @@
         <v>0.22377037514248421</v>
       </c>
       <c r="H89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I89">
         <v>1.5998818890829498E-2</v>
@@ -9808,10 +9805,10 @@
         <v>1.2983142117043279E-2</v>
       </c>
       <c r="AA89" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AB89" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AC89">
         <v>3.0655049338652131E-2</v>
@@ -9823,15 +9820,15 @@
         <v>4.7629999999999999</v>
       </c>
       <c r="AF89" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="90" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B90">
         <v>32.935202999999987</v>
@@ -9852,7 +9849,7 @@
         <v>0.47484638198044671</v>
       </c>
       <c r="H90" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I90">
         <v>1.6712428534841499E-2</v>
@@ -9909,10 +9906,10 @@
         <v>1.173679945977942E-2</v>
       </c>
       <c r="AA90" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AB90" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AC90">
         <v>3.7971360381861573E-2</v>
@@ -9924,15 +9921,15 @@
         <v>4.609</v>
       </c>
       <c r="AF90" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG90" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="91" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B91">
         <v>40.765403000000063</v>
@@ -9953,7 +9950,7 @@
         <v>0.27993506832842391</v>
       </c>
       <c r="H91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I91">
         <v>1.8192569716462201E-2</v>
@@ -10010,10 +10007,10 @@
         <v>1.251173399996576E-2</v>
       </c>
       <c r="AA91" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AB91" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AC91">
         <v>3.8530964109781872E-2</v>
@@ -10025,15 +10022,15 @@
         <v>5.6840000000000002</v>
       </c>
       <c r="AF91" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B92">
         <v>33.626102999999979</v>
@@ -10054,7 +10051,7 @@
         <v>0.50335835363096493</v>
       </c>
       <c r="H92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I92">
         <v>1.9324037588157501E-2</v>
@@ -10111,10 +10108,10 @@
         <v>1.1674292357072709E-2</v>
       </c>
       <c r="AA92" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AB92" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AC92">
         <v>2.9547828925889669E-2</v>
@@ -10126,15 +10123,15 @@
         <v>6.1260000000000003</v>
       </c>
       <c r="AF92" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B93">
         <v>36.389703000000047</v>
@@ -10155,7 +10152,7 @@
         <v>0.71824263785459408</v>
       </c>
       <c r="H93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I93">
         <v>1.7660246966611701E-2</v>
@@ -10212,10 +10209,10 @@
         <v>1.1326253153782479E-2</v>
       </c>
       <c r="AA93" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB93" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AC93">
         <v>3.3891206117483551E-2</v>
@@ -10227,15 +10224,15 @@
         <v>5.7539999999999996</v>
       </c>
       <c r="AF93" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B94">
         <v>12.09426480310162</v>
@@ -10256,7 +10253,7 @@
         <v>0.4317364292043484</v>
       </c>
       <c r="H94" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I94">
         <v>5.1471191527256996E-3</v>
@@ -10313,10 +10310,10 @@
         <v>1.3033853225436889E-2</v>
       </c>
       <c r="AA94" t="s">
+        <v>135</v>
+      </c>
+      <c r="AB94" t="s">
         <v>136</v>
-      </c>
-      <c r="AB94" t="s">
-        <v>137</v>
       </c>
       <c r="AC94">
         <v>2.345470343697674E-2</v>
@@ -10328,15 +10325,15 @@
         <v>2.58</v>
       </c>
       <c r="AF94" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG94" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="95" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B95">
         <v>1.8567606144864821</v>
@@ -10357,7 +10354,7 @@
         <v>-2.1162659838724951E-2</v>
       </c>
       <c r="H95" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I95">
         <v>5.6707741998356003E-3</v>
@@ -10414,10 +10411,10 @@
         <v>6.9933342914469182E-3</v>
       </c>
       <c r="AA95" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AB95" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AC95">
         <v>5.3081142459015839E-3</v>
@@ -10429,15 +10426,15 @@
         <v>1.83</v>
       </c>
       <c r="AF95" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG95" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="96" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B96">
         <v>4.8386029999999538</v>
@@ -10458,7 +10455,7 @@
         <v>0.36388294347989741</v>
       </c>
       <c r="H96" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I96">
         <v>3.0818554697518001E-3</v>
@@ -10515,10 +10512,10 @@
         <v>6.427147985287783E-3</v>
       </c>
       <c r="AA96" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AB96" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AC96">
         <v>2.0725099601593629E-2</v>
@@ -10530,15 +10527,15 @@
         <v>1.2549999999999999</v>
       </c>
       <c r="AF96" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG96" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="97" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B97">
         <v>2.6743870004365529</v>
@@ -10559,7 +10556,7 @@
         <v>-3.7425420495775297E-2</v>
       </c>
       <c r="H97" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I97">
         <v>2.5604337885034999E-3</v>
@@ -10616,10 +10613,10 @@
         <v>1.086559501395566E-2</v>
       </c>
       <c r="AA97" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AB97" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AC97">
         <v>1.2758134700589511E-2</v>
@@ -10631,15 +10628,15 @@
         <v>0.96689999999999998</v>
       </c>
       <c r="AF97" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG97" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="98" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B98">
         <v>1.0686787173235179</v>
@@ -10660,7 +10657,7 @@
         <v>-1.6906076636629741E-2</v>
       </c>
       <c r="H98" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I98">
         <v>1.4565722409801E-3</v>
@@ -10717,10 +10714,10 @@
         <v>7.4019827518654498E-3</v>
       </c>
       <c r="AA98" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AB98" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AC98">
         <v>2.9907487316176472E-3</v>
@@ -10732,15 +10729,15 @@
         <v>1.36</v>
       </c>
       <c r="AF98" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG98" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="99" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B99">
         <v>2.128090734642579</v>
@@ -10761,7 +10758,7 @@
         <v>1.989148866124146E-2</v>
       </c>
       <c r="H99" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I99">
         <v>2.7106164519278002E-3</v>
@@ -10818,10 +10815,10 @@
         <v>9.7847739831515394E-3</v>
       </c>
       <c r="AA99" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AB99" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AC99">
         <v>1.06508209149789E-2</v>
@@ -10833,15 +10830,15 @@
         <v>0.94799999999999995</v>
       </c>
       <c r="AF99" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG99" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="100" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B100">
         <v>3.3730199665762601</v>
@@ -10862,7 +10859,7 @@
         <v>-9.6435433536921078E-3</v>
       </c>
       <c r="H100" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I100">
         <v>2.6924254068357999E-3</v>
@@ -10919,10 +10916,10 @@
         <v>1.3984993754355669E-2</v>
       </c>
       <c r="AA100" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AB100" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AC100">
         <v>7.2891696375112251E-3</v>
@@ -10934,15 +10931,15 @@
         <v>2.218</v>
       </c>
       <c r="AF100" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG100" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="101" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B101">
         <v>5.1211849308225554</v>
@@ -10963,7 +10960,7 @@
         <v>1.7524778016578368E-2</v>
       </c>
       <c r="H101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I101">
         <v>7.4418628349596002E-3</v>
@@ -11020,10 +11017,10 @@
         <v>1.5160780714711971E-2</v>
       </c>
       <c r="AA101" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AB101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AC101">
         <v>1.4426702166579359E-2</v>
@@ -11035,15 +11032,15 @@
         <v>1.909</v>
       </c>
       <c r="AF101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="102" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B102">
         <v>3.6412393566752281</v>
@@ -11064,7 +11061,7 @@
         <v>-2.2532852801029731E-2</v>
       </c>
       <c r="H102" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I102">
         <v>6.6685031569578002E-3</v>
@@ -11121,10 +11118,10 @@
         <v>1.4550961209047831E-2</v>
       </c>
       <c r="AA102" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AB102" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AC102">
         <v>6.4754245644885388E-3</v>
@@ -11136,15 +11133,15 @@
         <v>2.923</v>
       </c>
       <c r="AF102" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG102" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="103" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B103">
         <v>24.618805640014219</v>
@@ -11165,7 +11162,7 @@
         <v>-2.7327692906827569E-2</v>
       </c>
       <c r="H103" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I103">
         <v>3.0928720163721599E-2</v>
@@ -11222,10 +11219,10 @@
         <v>1.6063427301705461E-2</v>
       </c>
       <c r="AA103" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AB103" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AC103">
         <v>5.7471459129687E-2</v>
@@ -11237,15 +11234,15 @@
         <v>2.3358287</v>
       </c>
       <c r="AF103" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG103" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="104" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B104">
         <v>2.1928091886750778</v>
@@ -11266,7 +11263,7 @@
         <v>-2.141443624246531E-2</v>
       </c>
       <c r="H104" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I104">
         <v>6.4991224345745998E-3</v>
@@ -11323,10 +11320,10 @@
         <v>8.2918905640863728E-3</v>
       </c>
       <c r="AA104" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AB104" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AC104">
         <v>5.7173843758252909E-3</v>
@@ -11338,15 +11335,15 @@
         <v>1.9690000000000001</v>
       </c>
       <c r="AF104" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG104" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="105" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B105">
         <v>3.231367342839762</v>
@@ -11367,7 +11364,7 @@
         <v>-3.8417362820798162E-2</v>
       </c>
       <c r="H105" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I105">
         <v>3.5370956769755998E-3</v>
@@ -11424,10 +11421,10 @@
         <v>7.9421060831501647E-3</v>
       </c>
       <c r="AA105" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AB105" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AC105">
         <v>6.2332263022026428E-3</v>
@@ -11439,15 +11436,15 @@
         <v>2.27</v>
       </c>
       <c r="AF105" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG105" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="106" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B106">
         <v>1.8058781556923531</v>
@@ -11468,7 +11465,7 @@
         <v>-3.261216640585024E-2</v>
       </c>
       <c r="H106" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I106">
         <v>3.4325729263321001E-3</v>
@@ -11525,10 +11522,10 @@
         <v>8.8206246141017304E-3</v>
       </c>
       <c r="AA106" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AB106" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AC106">
         <v>4.7038642323869607E-3</v>
@@ -11540,10 +11537,10 @@
         <v>1.9019999999999999</v>
       </c>
       <c r="AF106" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG106" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
